--- a/Capstone_Project/src/test/resources/testdata/LogData.xlsx
+++ b/Capstone_Project/src/test/resources/testdata/LogData.xlsx
@@ -3,19 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\umesh\OneDrive\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF330BB8-F787-4678-9B14-346ABA3F4C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{F1603DA3-90DD-4F72-B57E-D346C042BB1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{3660E3E4-58AB-4DCE-BFB3-64EF690C1CD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,10 +29,10 @@
     <t>password</t>
   </si>
   <si>
-    <t>johndoe01</t>
+    <t>Password123</t>
   </si>
   <si>
-    <t>Password123</t>
+    <t>johndoe08</t>
   </si>
 </sst>
 </file>
@@ -405,10 +401,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Capstone_Project/src/test/resources/testdata/LogData.xlsx
+++ b/Capstone_Project/src/test/resources/testdata/LogData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{F1603DA3-90DD-4F72-B57E-D346C042BB1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{243D3EF0-B66C-45CA-857D-D6A6F2111B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{3660E3E4-58AB-4DCE-BFB3-64EF690C1CD6}"/>
   </bookViews>
@@ -32,7 +32,7 @@
     <t>Password123</t>
   </si>
   <si>
-    <t>johndoe08</t>
+    <t>johndoe20</t>
   </si>
 </sst>
 </file>

--- a/Capstone_Project/src/test/resources/testdata/LogData.xlsx
+++ b/Capstone_Project/src/test/resources/testdata/LogData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{243D3EF0-B66C-45CA-857D-D6A6F2111B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{00684090-61B7-4C66-A258-B7293E712F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{3660E3E4-58AB-4DCE-BFB3-64EF690C1CD6}"/>
   </bookViews>
@@ -32,7 +32,7 @@
     <t>Password123</t>
   </si>
   <si>
-    <t>johndoe20</t>
+    <t>johndoe12345</t>
   </si>
 </sst>
 </file>

--- a/Capstone_Project/src/test/resources/testdata/LogData.xlsx
+++ b/Capstone_Project/src/test/resources/testdata/LogData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{00684090-61B7-4C66-A258-B7293E712F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{7FACCCDC-1F99-4B66-A5C7-D0A502A8D900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{3660E3E4-58AB-4DCE-BFB3-64EF690C1CD6}"/>
   </bookViews>
@@ -32,7 +32,7 @@
     <t>Password123</t>
   </si>
   <si>
-    <t>johndoe12345</t>
+    <t>johndoe321</t>
   </si>
 </sst>
 </file>

--- a/Capstone_Project/src/test/resources/testdata/LogData.xlsx
+++ b/Capstone_Project/src/test/resources/testdata/LogData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{7FACCCDC-1F99-4B66-A5C7-D0A502A8D900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{7F8DA4AE-D9A5-4160-BEB8-E90343DAE9E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{3660E3E4-58AB-4DCE-BFB3-64EF690C1CD6}"/>
   </bookViews>
@@ -32,7 +32,7 @@
     <t>Password123</t>
   </si>
   <si>
-    <t>johndoe321</t>
+    <t>joejohn321</t>
   </si>
 </sst>
 </file>

--- a/Capstone_Project/src/test/resources/testdata/LogData.xlsx
+++ b/Capstone_Project/src/test/resources/testdata/LogData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{7F8DA4AE-D9A5-4160-BEB8-E90343DAE9E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{E6FFB5BD-B5A8-4B5B-8E6D-E58A9D4EDF02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{3660E3E4-58AB-4DCE-BFB3-64EF690C1CD6}"/>
   </bookViews>
@@ -32,7 +32,7 @@
     <t>Password123</t>
   </si>
   <si>
-    <t>joejohn321</t>
+    <t>joejohn098</t>
   </si>
 </sst>
 </file>

--- a/Capstone_Project/src/test/resources/testdata/LogData.xlsx
+++ b/Capstone_Project/src/test/resources/testdata/LogData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{E6FFB5BD-B5A8-4B5B-8E6D-E58A9D4EDF02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{DC2966FA-DB6A-4FA4-93B2-AA83E0C32DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{3660E3E4-58AB-4DCE-BFB3-64EF690C1CD6}"/>
   </bookViews>

--- a/Capstone_Project/src/test/resources/testdata/LogData.xlsx
+++ b/Capstone_Project/src/test/resources/testdata/LogData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{DC2966FA-DB6A-4FA4-93B2-AA83E0C32DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{A5B4C986-4110-4918-950E-B0B8B409A4B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{3660E3E4-58AB-4DCE-BFB3-64EF690C1CD6}"/>
   </bookViews>
@@ -29,10 +29,10 @@
     <t>password</t>
   </si>
   <si>
-    <t>Password123</t>
+    <t>abc</t>
   </si>
   <si>
-    <t>joejohn098</t>
+    <t>joejohn555</t>
   </si>
 </sst>
 </file>

--- a/Capstone_Project/src/test/resources/testdata/LogData.xlsx
+++ b/Capstone_Project/src/test/resources/testdata/LogData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{A5B4C986-4110-4918-950E-B0B8B409A4B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{32532D7D-3BFD-4684-99F0-6B760B01A282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{3660E3E4-58AB-4DCE-BFB3-64EF690C1CD6}"/>
   </bookViews>

--- a/Capstone_Project/src/test/resources/testdata/LogData.xlsx
+++ b/Capstone_Project/src/test/resources/testdata/LogData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{32532D7D-3BFD-4684-99F0-6B760B01A282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{7F2C3376-1160-4657-A8D4-C292EAA46A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{3660E3E4-58AB-4DCE-BFB3-64EF690C1CD6}"/>
   </bookViews>
@@ -29,10 +29,10 @@
     <t>password</t>
   </si>
   <si>
-    <t>abc</t>
+    <t>joejohn222</t>
   </si>
   <si>
-    <t>joejohn555</t>
+    <t>Password123</t>
   </si>
 </sst>
 </file>
@@ -401,10 +401,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
